--- a/mapping/PDTD_DTM/Mapping_FCT_CLOS_LOAN_DISBURSEMENT.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_CLOS_LOAN_DISBURSEMENT.xlsx
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Fact giải ngân khoản vay T24 (grain hợp đồng), bổ sung liên kết hồ sơ CLOS qua SEAB_LOS_ID, vùng kinh doanh, nhóm nợ, nhóm khách hàng</t>
+          <t>Bảng FACT đối chiếu T24, hoàn toàn MỚI ở tầng PDTD_DTM — lưu khoản vay đã giải ngân của hệ CLOS, nối ngược về hồ sơ LOS qua SEAB_LOS_ID</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B3" s="19" t="inlineStr">
         <is>
-          <t>DAYID + CONTRACT</t>
+          <t>DAYID + T24_CONTRACT</t>
         </is>
       </c>
       <c r="E3" s="52" t="inlineStr">
@@ -911,57 +911,57 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>T24_CUSTOMER_SK</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Mã hợp đồng khoản vay</t>
+          <t>Khóa khách hàng T24</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — mã hợp đồng khoản vay</t>
+          <t>ĐỔI TÊN từ CUSTOMER_SK (rõ nghĩa chân khách hàng T24) — khóa tới DIM_T24_CUSTOMER</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>A.CONTRACT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+          <t>A.CUSTOMER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_SK</t>
+          <t>T24_CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới khách hàng T24</t>
+          <t>Mã khách hàng T24</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_T24_CUSTOMER</t>
+          <t>CỘT MỚI — BK cạnh SK, mã khách hàng T24, giá trị đã có sẵn trong bước lookup T24_CUSTOMER_SK</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>A.CUSTOMER_SK</t>
+          <t>A.CUSTOMER_CODE</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới đơn vị kinh doanh T24</t>
+          <t>Khóa đơn vị kinh doanh T24</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
@@ -992,379 +992,460 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>CONTRACT_SK</t>
+          <t>T24_COMPANY_CODE</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Mã đơn vị kinh doanh T24</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, mã công ty/chi nhánh T24, giá trị đã có sẵn trong bước lookup T24_COMPANY_SK</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>A.CO_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>T24_CONTRACT_SK</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới hợp đồng T24</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_T24_LOAN</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Khóa hợp đồng T24</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>ĐỔI TÊN từ CONTRACT_SK (rõ nghĩa chân T24) — khóa tới DIM_T24_LOAN</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.CONTRACT_SK</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>SEAB_PRODUCTS_DE_SK</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>T24_CONTRACT</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã hợp đồng khoản vay</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>PK (2/2) — ĐỔI TÊN từ CONTRACT, chuyển vị trí xuống ngay sau T24_CONTRACT_SK để đồng bộ nhóm BK cạnh SK — mã hợp đồng khoản vay</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>A.CONTRACT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>T24_SEAB_PRODUCTS_DE_SK</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới sản phẩm T24</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_T24_SEAB_PRODUCTS_DE</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Khóa sản phẩm T24</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>ĐỔI TÊN từ SEAB_PRODUCTS_DE_SK (rõ nghĩa chân T24) — khóa tới DIM_T24_SEAB_PRODUCTS_DE</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.SEAB_PRODUCTS_DE_SK</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>APPLICATION_SK</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_APPLICATION, tra theo SEAB_LOS_ID</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C ON C.WI_NAME = A.SEAB_LOS_ID → C.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>SEAB_LOS_ID</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>T24_SEAB_PRODUCTS_DE</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ LOS</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ LOS do T24 lưu, gắn với hợp đồng</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>A.SEAB_LOS_ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>ZONE</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(50)</t>
-        </is>
-      </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Vùng kinh doanh</t>
+          <t>Mã sản phẩm T24</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Tên vùng của đơn vị kinh doanh</t>
+          <t>CỘT MỚI — BK cạnh SK, giá trị đã có sẵn trong bước lookup T24_SEAB_PRODUCTS_DE_SK</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN D ON D.COMPANY_CODE = A.CO_CODE → D.VUNG</t>
+          <t>A.SEAB_PRODUCTS_DE</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>DISBURSEMENT_AMT</t>
+          <t>APPLICATION_SK</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(20,2)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Số tiền giải ngân</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Số tiền giải ngân</t>
+          <t>Khóa tới DIM_CLOS_APPLICATION, tra theo SEAB_LOS_ID</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>ABS(A.FIRST_DISBURSEMENT_AMT)</t>
+          <t>LEFT JOIN C ON C.WI_NAME = A.SEAB_LOS_ID → C.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>CUR_BALANCE</t>
+          <t>SEAB_LOS_ID</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(20,2)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Dư nợ hiện tại</t>
+          <t>Mã hồ sơ LOS</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Dư nợ hiện tại</t>
+          <t>Mã hồ sơ LOS do T24 lưu, gắn với hợp đồng</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>(ABS(NVL(A.BALANCE,0)) + ABS(NVL(A.PD_BALANCE,0))) * A.REVAL_RATE</t>
+          <t>A.SEAB_LOS_ID</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
+          <t>ZONE</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Vùng kinh doanh</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>Tên vùng của đơn vị kinh doanh</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>LEFT JOIN D ON D.COMPANY_CODE = A.CO_CODE → D.VUNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>DISBURSEMENT_AMT</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(20,2)</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Số tiền giải ngân</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Số tiền giải ngân</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>ABS(A.FIRST_DISBURSEMENT_AMT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>CUR_BALANCE</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(20,2)</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Dư nợ hiện tại</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Dư nợ hiện tại</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>(ABS(NVL(A.BALANCE,0)) + ABS(NVL(A.PD_BALANCE,0))) * A.REVAL_RATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
           <t>NO_DAYS_OVERDUE</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>NUMBER(6)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Số ngày quá hạn</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Số ngày quá hạn — self-join chính bảng driving qua PD_CONTRACT</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN I ON I.CONTRACT = A.PD_CONTRACT → I.NO_DAYS_OVERDUE</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>CUR_BUCKET</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>NUMBER(2)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Nhóm nợ</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>Nhóm nợ — cùng self-join PD_CONTRACT như NO_DAYS_OVERDUE, dùng chung alias I</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN I ON I.CONTRACT = A.PD_CONTRACT → CASE WHEN I.NO_DAYS_OVERDUE &gt; 360 THEN 5 WHEN I.NO_DAYS_OVERDUE &gt; 180 THEN 4 WHEN I.NO_DAYS_OVERDUE &gt; 90 THEN 3 WHEN I.NO_DAYS_OVERDUE &gt;= 10 THEN 2 ELSE 1 END</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>LIMIT_REFERENCE</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Mã hạn mức</t>
         </is>
       </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Mã hạn mức — giữ trên fact (không chuyển DIM_T24_LOAN) vì nguồn là chính STG_FCT_LOAN</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Mã hạn mức — giữ trên fact (không chuyển DIM_T24_LOAN) vì nguồn là chính STG_FCT_LOAN, không phải STG_DIM_LOAN</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>A.LIMIT_REF</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>CUST_GROUP</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Nhóm khách hàng</t>
         </is>
       </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Nhóm khách hàng — đi qua CUSTOMER_CODE của DIM_CLOS_APPLICATION, lookup STG_DIM_CLOS_CUSTOMER theo NK=CUSTOMER_CODE, lấy bản ghi hiệu lực EXP_DATE IS NULL</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>Nhóm khách hàng — đi qua CUSTOMER_CODE của DIM_CLOS_APPLICATION, lookup STG_DIM_CLOS_CUSTOMER theo NK=CUSTOMER_CODE</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN E2 ON E2.CUSTOMER_CODE = C.CUSTOMER_CODE AND E2.EXP_DATE IS NULL → E2.CUST_GROUP</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>LOANCASEID</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>Mã khoản vay hồ sơ cha</t>
         </is>
       </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>Mã khoản vay gắn với hồ sơ cha — chỉ giữ khi CHANGE_REQUEST='New' (đúng SRS BC11), còn lại NULL dù DIM có giá trị</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Mã khoản vay gắn với hồ sơ cha — chỉ giữ khi CHANGE_REQUEST='New' (đúng SRS BC11)</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN F ON F.WI_NAME = C.WI_NAME → CASE WHEN F.CHANGE_REQUEST = 'New' THEN C.LOANCASEID ELSE NULL END</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>APPROVAL_WINAME_LOS</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Mã hồ sơ cha đã phê duyệt</t>
         </is>
       </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ cha đã được phê duyệt — tra qua window function MIN(WI_NAME) OVER (PARTITION BY LOANCASEID) trên STG_DIM_CLOS_APPLICATION, JOIN theo SEAB_LOS_ID=WI_NAME</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ cha đã được phê duyệt — tra qua window function MIN(WI_NAME) OVER (PARTITION BY LOANCASEID)</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN (SELECT WI_NAME, MIN(WI_NAME) OVER (PARTITION BY LOANCASEID) AS FIRST_APPROVED_WI_NAME FROM C WHERE C.EXP_DATE IS NULL) SUB_APPROVAL ON SUB_APPROVAL.WI_NAME = A.SEAB_LOS_ID → SUB_APPROVAL.FIRST_APPROVED_WI_NAME</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="105" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
+    <row r="37" ht="105" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>APPROVAL_DATE</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Ngày phê duyệt</t>
         </is>
       </c>
-      <c r="D34" s="54" t="inlineStr">
-        <is>
-          <t>Ngày phê duyệt — MAX(EXITDATE) tại bước CreditApproval/CreditCommittee với quyết định Submit/Send To HOSupport/Send To PostSanction, JOIN theo SEAB_LOS_ID=WI_NAME</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>Ngày phê duyệt — MAX(EXITDATE) tại bước CreditApproval/CreditCommittee với quyết định hoàn tất</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN (SELECT G2.WI_NAME, MAX(G2.EXITDATE) AS APPROVED_DATE FROM G G2 LEFT JOIN H ON H.DIMENSION_KEY = G2.WORKSTEP_DECISION_SK WHERE G2.USERNAME IS NOT NULL AND G2.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND H.DECISION_CODE IN ('Submit','Send To HOSupport','Send To PostSanction') GROUP BY G2.WI_NAME) SUB_APPROVED ON SUB_APPROVED.WI_NAME = A.SEAB_LOS_ID → SUB_APPROVED.APPROVED_DATE</t>
         </is>
